--- a/00 Raw data/SDG/Publications_by_SDG_-_National_Formosa_University.xlsx
+++ b/00 Raw data/SDG/Publications_by_SDG_-_National_Formosa_University.xlsx
@@ -90,7 +90,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2018 to 2025</t>
+          <t>2017 to 2025</t>
         </is>
       </c>
     </row>
@@ -157,7 +157,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8 July 2026</t>
+          <t>5 August 2026</t>
         </is>
       </c>
     </row>
@@ -169,7 +169,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16 July 2026</t>
+          <t>13 August 2026</t>
         </is>
       </c>
     </row>
@@ -225,13 +225,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="C14" t="n">
-        <v>0.57</v>
+        <v>0.56</v>
       </c>
       <c r="D14" t="n">
-        <v>75.0</v>
+        <v>93.0</v>
       </c>
     </row>
     <row r="15">
@@ -241,13 +241,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>123.0</v>
+        <v>135.0</v>
       </c>
       <c r="C15" t="n">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="D15" t="n">
-        <v>2219.0</v>
+        <v>2668.0</v>
       </c>
     </row>
     <row r="16">
@@ -257,13 +257,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>46.0</v>
+        <v>54.0</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="D16" t="n">
-        <v>466.0</v>
+        <v>512.0</v>
       </c>
     </row>
     <row r="17">
@@ -292,10 +292,10 @@
         <v>15.0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="D18" t="n">
-        <v>74.0</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="19">
@@ -305,13 +305,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>205.0</v>
+        <v>228.0</v>
       </c>
       <c r="C19" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="D19" t="n">
-        <v>1279.0</v>
+        <v>1694.0</v>
       </c>
     </row>
     <row r="20">
@@ -321,13 +321,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>36.0</v>
+        <v>38.0</v>
       </c>
       <c r="C20" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="D20" t="n">
-        <v>571.0</v>
+        <v>608.0</v>
       </c>
     </row>
     <row r="21">
@@ -337,13 +337,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>261.0</v>
+        <v>286.0</v>
       </c>
       <c r="C21" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="D21" t="n">
-        <v>1937.0</v>
+        <v>2450.0</v>
       </c>
     </row>
     <row r="22">
@@ -356,10 +356,10 @@
         <v>2.0</v>
       </c>
       <c r="C22" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="D22" t="n">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="23">
@@ -369,13 +369,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="C23" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="D23" t="n">
-        <v>238.0</v>
+        <v>248.0</v>
       </c>
     </row>
     <row r="24">
@@ -385,13 +385,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>60.0</v>
+        <v>61.0</v>
       </c>
       <c r="C24" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="D24" t="n">
-        <v>874.0</v>
+        <v>911.0</v>
       </c>
     </row>
     <row r="25">
@@ -401,13 +401,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="C25" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="D25" t="n">
-        <v>275.0</v>
+        <v>310.0</v>
       </c>
     </row>
     <row r="26">
@@ -420,10 +420,10 @@
         <v>7.0</v>
       </c>
       <c r="C26" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="D26" t="n">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="27">
@@ -436,10 +436,10 @@
         <v>14.0</v>
       </c>
       <c r="C27" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="D27" t="n">
-        <v>80.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="28">
@@ -452,10 +452,10 @@
         <v>11.0</v>
       </c>
       <c r="C28" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="D28" t="n">
-        <v>108.0</v>
+        <v>109.0</v>
       </c>
     </row>
     <row r="29">
@@ -465,13 +465,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>663.0</v>
+        <v>732.0</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="D29" t="n">
-        <v>6164.0</v>
+        <v>7613.0</v>
       </c>
     </row>
     <row r="30">
